--- a/resource/模板文件/文书模板/用工单位汇总.xlsx
+++ b/resource/模板文件/文书模板/用工单位汇总.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>公司名称汇总</t>
+          <t>用工单位汇总</t>
         </is>
       </c>
     </row>
